--- a/back_end/data/warehouse/견우오아시스.xlsx
+++ b/back_end/data/warehouse/견우오아시스.xlsx
@@ -23,7 +23,7 @@
     <t>조회기간 :</t>
   </si>
   <si>
-    <t>2026-05-29 ~ 2026-05-29</t>
+    <t>2026-06-05 ~ 2026-06-05</t>
   </si>
   <si>
     <t>수탁품명</t>
@@ -78,42 +78,6 @@
     <t>C/T No.</t>
   </si>
   <si>
-    <t>꽃갈비(EX)CH/86R</t>
-  </si>
-  <si>
-    <t>28.6</t>
-  </si>
-  <si>
-    <t>BOX</t>
-  </si>
-  <si>
-    <t>ONEYRICGD8143400</t>
-  </si>
-  <si>
-    <t>2026-05-22</t>
-  </si>
-  <si>
-    <t>50中</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2028-02-24</t>
-  </si>
-  <si>
-    <t>미국</t>
-  </si>
-  <si>
-    <t>86R</t>
-  </si>
-  <si>
-    <t>EX</t>
-  </si>
-  <si>
-    <t>1430KG(가중량)</t>
-  </si>
-  <si>
     <t xml:space="preserve">소     계</t>
   </si>
   <si>
@@ -126,7 +90,7 @@
     <t>1/1</t>
   </si>
   <si>
-    <t>2026-05-29 09:17:25</t>
+    <t>2026-06-05 09:32:49</t>
   </si>
 </sst>
 </file>
@@ -281,7 +245,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -290,10 +254,10 @@
     <xf numFmtId="4" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -763,75 +727,41 @@
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1">
-      <c t="s" r="A6" s="7">
-        <v>22</v>
-      </c>
+      <c r="A6" s="7"/>
       <c r="B6" s="7"/>
-      <c t="s" r="C6" s="7">
-        <v>23</v>
-      </c>
-      <c t="s" r="D6" s="7">
-        <v>24</v>
-      </c>
-      <c r="E6" s="8">
-        <v>38</v>
-      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="8"/>
       <c r="F6" s="8"/>
-      <c r="G6" s="9">
-        <v>1086.8</v>
-      </c>
-      <c t="s" r="H6" s="7">
-        <v>25</v>
-      </c>
+      <c r="G6" s="9"/>
+      <c r="H6" s="7"/>
       <c r="I6" s="7"/>
-      <c t="s" r="J6" s="10">
-        <v>26</v>
-      </c>
+      <c r="J6" s="10"/>
       <c r="K6" s="10"/>
-      <c t="s" r="L6" s="7">
-        <v>27</v>
-      </c>
+      <c r="L6" s="7"/>
       <c r="M6" s="10"/>
       <c r="N6" s="10"/>
       <c r="O6" s="10"/>
-      <c t="s" r="P6" s="10">
-        <v>28</v>
-      </c>
+      <c r="P6" s="10"/>
       <c r="Q6" s="10"/>
-      <c t="s" r="R6" s="10">
-        <v>29</v>
-      </c>
-      <c r="S6" s="8">
-        <v>636</v>
-      </c>
-      <c t="s" r="T6" s="7">
-        <v>30</v>
-      </c>
-      <c t="s" r="U6" s="7">
-        <v>31</v>
-      </c>
+      <c r="R6" s="10"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
       <c r="V6" s="7"/>
-      <c t="s" r="W6" s="7">
-        <v>32</v>
-      </c>
-      <c t="s" r="X6" s="11">
-        <v>33</v>
-      </c>
+      <c r="W6" s="7"/>
+      <c r="X6" s="11"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c t="s" r="A7" s="12">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
       <c r="D7" s="12"/>
-      <c r="E7" s="13">
-        <v>38</v>
-      </c>
+      <c r="E7" s="13"/>
       <c r="F7" s="13"/>
-      <c r="G7" s="14">
-        <v>1086.8</v>
-      </c>
+      <c r="G7" s="14"/>
       <c r="H7" s="15"/>
       <c r="I7" s="15"/>
       <c r="J7" s="15"/>
@@ -852,18 +782,14 @@
     </row>
     <row r="8" ht="18" customHeight="1">
       <c t="s" r="A8" s="16">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
       <c r="D8" s="16"/>
-      <c r="E8" s="17">
-        <v>38</v>
-      </c>
+      <c r="E8" s="17"/>
       <c r="F8" s="17"/>
-      <c r="G8" s="18">
-        <v>1086.8</v>
-      </c>
+      <c r="G8" s="18"/>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
       <c r="J8" s="19"/>
@@ -885,14 +811,14 @@
     <row r="9" ht="5.25" customHeight="1"/>
     <row r="10" ht="1.5" customHeight="1">
       <c t="s" r="A10" s="20">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
       <c t="s" r="K10" s="21">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="L10" s="21"/>
       <c r="M10" s="21"/>
@@ -907,7 +833,7 @@
       <c r="L11" s="21"/>
       <c r="M11" s="21"/>
       <c t="s" r="V11" s="22">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="W11" s="22"/>
       <c r="X11" s="22"/>
